--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0003T0006Z000C1N64_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0003T0006Z000C1N64_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>62.46566941159777</v>
+        <v>10.15067127938464</v>
       </c>
       <c r="D2" t="n">
-        <v>49.26851378148365</v>
+        <v>8.006133489491093</v>
       </c>
       <c r="E2" t="n">
-        <v>18.43933598305141</v>
+        <v>2.996392097245854</v>
       </c>
       <c r="F2" t="n">
-        <v>18.68433979563909</v>
+        <v>3.036205216791352</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>20.47804878057016</v>
+        <v>3.327682926842651</v>
       </c>
       <c r="D3" t="n">
-        <v>18.33712082089225</v>
+        <v>2.979782133394991</v>
       </c>
       <c r="E3" t="n">
-        <v>18.43933598305141</v>
+        <v>2.996392097245854</v>
       </c>
       <c r="F3" t="n">
-        <v>18.68433979563909</v>
+        <v>3.036205216791352</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>11.06340833709339</v>
+        <v>1.797803854777675</v>
       </c>
       <c r="D4" t="n">
-        <v>13.18253533726631</v>
+        <v>2.142161992305776</v>
       </c>
       <c r="E4" t="n">
-        <v>18.43933598305141</v>
+        <v>2.996392097245854</v>
       </c>
       <c r="F4" t="n">
-        <v>18.68433979563909</v>
+        <v>3.036205216791352</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>23.55492746148821</v>
+        <v>3.827675712491835</v>
       </c>
       <c r="D5" t="n">
-        <v>5.688510073175037</v>
+        <v>0.9243828868909435</v>
       </c>
       <c r="E5" t="n">
-        <v>18.43933598305141</v>
+        <v>2.996392097245854</v>
       </c>
       <c r="F5" t="n">
-        <v>18.68433979563909</v>
+        <v>3.036205216791352</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>21.74031800837005</v>
+        <v>3.532801676360132</v>
       </c>
       <c r="D6" t="n">
-        <v>4.79021717206596</v>
+        <v>0.7784102904607185</v>
       </c>
       <c r="E6" t="n">
-        <v>18.43933598305141</v>
+        <v>2.996392097245854</v>
       </c>
       <c r="F6" t="n">
-        <v>18.68433979563909</v>
+        <v>3.036205216791352</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>37.59178081505973</v>
+        <v>6.108664382447206</v>
       </c>
       <c r="D7" t="n">
-        <v>21.27204738618265</v>
+        <v>3.456707700254681</v>
       </c>
       <c r="E7" t="n">
-        <v>18.43933598305141</v>
+        <v>2.996392097245854</v>
       </c>
       <c r="F7" t="n">
-        <v>18.68433979563909</v>
+        <v>3.036205216791352</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>5.616133727920525</v>
+        <v>0.9126217307870854</v>
       </c>
       <c r="D8" t="n">
-        <v>34.58286285009628</v>
+        <v>5.619715213140645</v>
       </c>
       <c r="E8" t="n">
-        <v>18.43933598305141</v>
+        <v>2.996392097245854</v>
       </c>
       <c r="F8" t="n">
-        <v>18.68433979563909</v>
+        <v>3.036205216791352</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>22.94501326788684</v>
+        <v>3.728564656031612</v>
       </c>
       <c r="D9" t="n">
-        <v>16.71868950573221</v>
+        <v>2.716787044681484</v>
       </c>
       <c r="E9" t="n">
-        <v>18.43933598305141</v>
+        <v>2.996392097245854</v>
       </c>
       <c r="F9" t="n">
-        <v>18.68433979563909</v>
+        <v>3.036205216791352</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>2.628100866526956</v>
+        <v>0.4270663908106304</v>
       </c>
       <c r="D10" t="n">
-        <v>3.425976527511901</v>
+        <v>0.5567211857206839</v>
       </c>
       <c r="E10" t="n">
-        <v>18.43933598305141</v>
+        <v>2.996392097245854</v>
       </c>
       <c r="F10" t="n">
-        <v>18.68433979563909</v>
+        <v>3.036205216791352</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>26.15292492706745</v>
+        <v>4.24985030064846</v>
       </c>
       <c r="D11" t="n">
-        <v>27.70177355436485</v>
+        <v>4.501538202584288</v>
       </c>
       <c r="E11" t="n">
-        <v>18.43933598305141</v>
+        <v>2.996392097245854</v>
       </c>
       <c r="F11" t="n">
-        <v>18.68433979563909</v>
+        <v>3.036205216791352</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>13.49653331405995</v>
+        <v>2.193186663534742</v>
       </c>
       <c r="D12" t="n">
-        <v>12.59478645013263</v>
+        <v>2.046652798146552</v>
       </c>
       <c r="E12" t="n">
-        <v>18.43933598305141</v>
+        <v>2.996392097245854</v>
       </c>
       <c r="F12" t="n">
-        <v>18.68433979563909</v>
+        <v>3.036205216791352</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>41.32998705049862</v>
+        <v>6.716122895706026</v>
       </c>
       <c r="D13" t="n">
-        <v>41.36014594417428</v>
+        <v>6.72102371592832</v>
       </c>
       <c r="E13" t="n">
-        <v>18.43933598305141</v>
+        <v>2.996392097245854</v>
       </c>
       <c r="F13" t="n">
-        <v>18.68433979563909</v>
+        <v>3.036205216791352</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>47.20942748461928</v>
+        <v>7.671531966250634</v>
       </c>
       <c r="D14" t="n">
-        <v>46.08570985908301</v>
+        <v>7.488927852100989</v>
       </c>
       <c r="E14" t="n">
-        <v>18.43933598305141</v>
+        <v>2.996392097245854</v>
       </c>
       <c r="F14" t="n">
-        <v>18.68433979563909</v>
+        <v>3.036205216791352</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>42.70723909583992</v>
+        <v>6.939926353073987</v>
       </c>
       <c r="D15" t="n">
-        <v>42.90367334489095</v>
+        <v>6.971846918544779</v>
       </c>
       <c r="E15" t="n">
-        <v>18.43933598305141</v>
+        <v>2.996392097245854</v>
       </c>
       <c r="F15" t="n">
-        <v>18.68433979563909</v>
+        <v>3.036205216791352</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>43.67654301923019</v>
+        <v>7.097438240624907</v>
       </c>
       <c r="D16" t="n">
-        <v>43.65399507022862</v>
+        <v>7.093774198912151</v>
       </c>
       <c r="E16" t="n">
-        <v>18.43933598305141</v>
+        <v>2.996392097245854</v>
       </c>
       <c r="F16" t="n">
-        <v>18.68433979563909</v>
+        <v>3.036205216791352</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>24.54225579427393</v>
+        <v>3.988116566569515</v>
       </c>
       <c r="D17" t="n">
-        <v>24.93962677400457</v>
+        <v>4.052689350775743</v>
       </c>
       <c r="E17" t="n">
-        <v>18.43933598305141</v>
+        <v>2.996392097245854</v>
       </c>
       <c r="F17" t="n">
-        <v>18.68433979563909</v>
+        <v>3.036205216791352</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>48.26488338315362</v>
+        <v>7.843043549762464</v>
       </c>
       <c r="D18" t="n">
-        <v>48.86331158827413</v>
+        <v>7.940288133094547</v>
       </c>
       <c r="E18" t="n">
-        <v>18.43933598305141</v>
+        <v>2.996392097245854</v>
       </c>
       <c r="F18" t="n">
-        <v>18.68433979563909</v>
+        <v>3.036205216791352</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>53.69826717943839</v>
+        <v>8.725968416658738</v>
       </c>
       <c r="D19" t="n">
-        <v>53.84267322125666</v>
+        <v>8.749434398454207</v>
       </c>
       <c r="E19" t="n">
-        <v>18.43933598305141</v>
+        <v>2.996392097245854</v>
       </c>
       <c r="F19" t="n">
-        <v>18.68433979563909</v>
+        <v>3.036205216791352</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>64.28485487831314</v>
+        <v>10.44628891772589</v>
       </c>
       <c r="D20" t="n">
-        <v>64.3285912219179</v>
+        <v>10.45339607356166</v>
       </c>
       <c r="E20" t="n">
-        <v>18.43933598305141</v>
+        <v>2.996392097245854</v>
       </c>
       <c r="F20" t="n">
-        <v>18.68433979563909</v>
+        <v>3.036205216791352</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>58.93469776189612</v>
+        <v>9.57688838630812</v>
       </c>
       <c r="D21" t="n">
-        <v>59.36768035852289</v>
+        <v>9.64724805825997</v>
       </c>
       <c r="E21" t="n">
-        <v>18.43933598305141</v>
+        <v>2.996392097245854</v>
       </c>
       <c r="F21" t="n">
-        <v>18.68433979563909</v>
+        <v>3.036205216791352</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
